--- a/SSC7/Grading/2 stage/6-examples/SSC7_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/SSC7/Grading/2 stage/6-examples/SSC7_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="17640" yWindow="-21000" windowWidth="30240" windowHeight="17300" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SSC7" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gemini Generation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SSC7" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="C1" s="23" t="inlineStr">
         <is>
-          <t>GPT-5 Generation</t>
+          <t>Grading</t>
         </is>
       </c>
       <c r="D1" s="23" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>Represented as [*] --&gt; Shopping where Shopping is the main composite state equivalent to Active</t>
+          <t>Initial state points to Shopping which is equivalent to Active</t>
         </is>
       </c>
       <c r="E2" s="6" t="n"/>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="D3" s="28" t="inlineStr">
         <is>
-          <t>Represented by Shopping composite state which contains all main operational substates</t>
+          <t>Shopping is a composite state equivalent to Active</t>
         </is>
       </c>
       <c r="E3" s="6" t="n"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Represented as [*] --&gt; ReadyForNextItem within Shopping composite state</t>
+          <t>Initial state inside Shopping points to Ready</t>
         </is>
       </c>
       <c r="E4" s="6" t="n"/>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>Represented as ReadyForNextItem state</t>
+          <t>Ready state is present</t>
         </is>
       </c>
       <c r="E5" s="6" t="n"/>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Represented as barcodeScanned(code) [!barcodeExists(code)] / showError() self-transition on ReadyForNextItem</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E6" s="6" t="n"/>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>Represented as [!barcodeExists(code)] guard condition</t>
+          <t>Guard present</t>
         </is>
       </c>
       <c r="E7" s="6" t="n"/>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>Represented as showError() action</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E8" s="6" t="n"/>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>Represented as productCodeEntered(code) [!productCodeExists(code)] / showError() self-transition</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E9" s="6" t="n"/>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>Represented as [!productCodeExists(code)] guard condition</t>
+          <t>Guard present</t>
         </is>
       </c>
       <c r="E10" s="6" t="n"/>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>Represented as showError() action</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>Represented as productCodeEntered(code) [productCodeExists(code)] / requestItemWeight(code) to WeighingProductCodeItem</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>Represented as [productCodeExists(code)] guard condition</t>
+          <t>Guard present</t>
         </is>
       </c>
       <c r="E13" s="6" t="n"/>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>Represented as barcodeScanned(code) [barcodeExists(code)] / showItem(code) to AwaitingSecurityCheck</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E14" s="6" t="n"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="D15" s="28" t="inlineStr">
         <is>
-          <t>Represented as [barcodeExists(code)] guard condition</t>
+          <t>Guard present</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>Represented as showItem(code) which displays the item after adding it</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>Represented as cancelEverything transition from ReadyForNextItem to OverrideClearAll</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E17" s="6" t="n"/>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>Represented by routing to OverrideClearAll substate which handles clearing everything</t>
+          <t>Handled implicitly by using separate override states</t>
         </is>
       </c>
       <c r="E18" s="6" t="n"/>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="D19" s="28" t="inlineStr">
         <is>
-          <t>Represented as removeItem transition from ReadyForNextItem to OverrideClearItem</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E19" s="6" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>Represented as [billHasItems()] guard condition</t>
+          <t>Guard present</t>
         </is>
       </c>
       <c r="E20" s="6" t="n"/>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="D21" s="28" t="inlineStr">
         <is>
-          <t>Represented by routing to OverrideClearItem substate which handles clearing a single item</t>
+          <t>Handled implicitly by using separate override states</t>
         </is>
       </c>
       <c r="E21" s="6" t="n"/>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>Represented as ownBags transition from ReadyForNextItem to WeighingBag</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E22" s="6" t="n"/>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="D23" s="28" t="inlineStr">
         <is>
-          <t>Represented as pay transition from ReadyForNextItem to PaymentProcessing</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E23" s="6" t="n"/>
@@ -6795,7 +6795,7 @@
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>Represented as [billHasItems()] guard condition</t>
+          <t>Guard present</t>
         </is>
       </c>
       <c r="E24" s="6" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="D25" s="28" t="inlineStr">
         <is>
-          <t>Represented as entry action in PaymentProcessing state note</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E25" s="6" t="n"/>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>Represented as WeighingProductCodeItem state</t>
+          <t>State present</t>
         </is>
       </c>
       <c r="E26" s="6" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D27" s="28" t="inlineStr">
         <is>
-          <t>Represented as cancel transition from WeighingProductCodeItem to ReadyForNextItem</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E27" s="6" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>Represented as itemWeightReceived(weight) transition from WeighingProductCodeItem to AwaitingSecurityCheck</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E28" s="6" t="n"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="D29" s="28" t="inlineStr">
         <is>
-          <t>Represented as showItemWithWeight(weight) action which displays the weighed item</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E29" s="6" t="n"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>Represented as AwaitingSecurityCheck state</t>
+          <t>State present</t>
         </is>
       </c>
       <c r="E30" s="6" t="n"/>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="D31" s="28" t="inlineStr">
         <is>
-          <t>Represented as securityWeightReceived(weight) [weightMatches(weight)] transition from AwaitingSecurityCheck to ReadyForNextItem</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E31" s="6" t="n"/>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>Represented as [weightMatches(weight)] guard condition</t>
+          <t>Guard present</t>
         </is>
       </c>
       <c r="E32" s="6" t="n"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>Represented as securityWeightReceived(weight) [!weightMatches(weight)] transition from AwaitingSecurityCheck to OverrideClearItem</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E33" s="6" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>Represented as [!weightMatches(weight)] guard condition</t>
+          <t>Guard present</t>
         </is>
       </c>
       <c r="E34" s="6" t="n"/>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D35" s="28" t="inlineStr">
         <is>
-          <t>Represented by routing to OverrideClearItem substate which handles clearing a single item</t>
+          <t>Handled implicitly by using separate override states</t>
         </is>
       </c>
       <c r="E35" s="6" t="n"/>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>Represented as cancelEverything transition from AwaitingSecurityCheck to OverrideClearAll</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E36" s="6" t="n"/>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="D37" s="28" t="inlineStr">
         <is>
-          <t>Represented by routing to OverrideClearAll substate which handles clearing everything</t>
+          <t>Handled implicitly by using separate override states</t>
         </is>
       </c>
       <c r="E37" s="6" t="n"/>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D38" s="25" t="inlineStr">
         <is>
-          <t>Represented as WeighingBag state</t>
+          <t>State present</t>
         </is>
       </c>
       <c r="E38" s="6" t="n"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="D39" s="28" t="inlineStr">
         <is>
-          <t>Represented as securityWeightReceived(weight) transition from WeighingBag to ReadyForNextItem</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E39" s="6" t="n"/>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>Represented as addBag(weight) action in the transition</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E40" s="6" t="n"/>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="D41" s="28" t="inlineStr">
         <is>
-          <t>Represented as cancel transition from WeighingBag to ReadyForNextItem</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E41" s="6" t="n"/>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>Represented as OverrideRequired composite state containing OverrideClearItem and OverrideClearAll substates</t>
+          <t>State present as a composite state</t>
         </is>
       </c>
       <c r="E42" s="6" t="n"/>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>Represented as entry / turnLightOn() in OverrideRequired state note</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E43" s="6" t="n"/>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>Represented as exit / turnLightOff() in OverrideRequired state note</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E44" s="6" t="n"/>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="D45" s="28" t="inlineStr">
         <is>
-          <t>Represented as staffCodeEntered(code) [overrideCodeValid(code)] / clearItemFromBill() from OverrideClearItem to ReadyForNextItem</t>
+          <t>Transitions go to Shopping which enters Ready</t>
         </is>
       </c>
       <c r="E45" s="6" t="n"/>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>Represented by transition from OverrideClearItem substate with [overrideCodeValid(code)] guard</t>
+          <t>Guard present and type handled by state</t>
         </is>
       </c>
       <c r="E46" s="6" t="n"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="D47" s="28" t="inlineStr">
         <is>
-          <t>Represented as clearItemFromBill() action</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E47" s="6" t="n"/>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D48" s="25" t="inlineStr">
         <is>
-          <t>Represented as staffCodeEntered(code) [overrideCodeValid(code)] / clearEverything() from OverrideClearAll to ReadyForNextItem</t>
+          <t>Transition goes to Shopping which enters Ready</t>
         </is>
       </c>
       <c r="E48" s="6" t="n"/>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D49" s="28" t="inlineStr">
         <is>
-          <t>Represented by transition from OverrideClearAll substate with [overrideCodeValid(code)] guard</t>
+          <t>Guard present and type handled by state</t>
         </is>
       </c>
       <c r="E49" s="6" t="n"/>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>Represented as clearEverything() action</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E50" s="6" t="n"/>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D51" s="28" t="inlineStr">
         <is>
-          <t>Represented as self-transitions on both OverrideClearItem and OverrideClearAll with [!overrideCodeValid(code)] guard</t>
+          <t>Self-transitions on incorrect code present</t>
         </is>
       </c>
       <c r="E51" s="6" t="n"/>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="D52" s="25" t="inlineStr">
         <is>
-          <t>Represented as [!overrideCodeValid(code)] guard condition</t>
+          <t>Guard present</t>
         </is>
       </c>
       <c r="E52" s="6" t="n"/>
@@ -7654,12 +7654,12 @@
     <row r="53" ht="12.75" customHeight="1" s="97">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Transition</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>error()</t>
+          <t>timeoutWarning (Active ⇒ TimeoutCountdown)</t>
         </is>
       </c>
       <c r="C53" s="29" t="n">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="D53" s="28" t="inlineStr">
         <is>
-          <t>Represented as timeoutWarning transition from Shopping to TimeoutWarning</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E53" s="6" t="n"/>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>timeoutWarning (Active ⇒ TimeoutCountdown)</t>
+          <t>error()</t>
         </is>
       </c>
       <c r="C54" s="24" t="n">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D54" s="25" t="inlineStr">
         <is>
-          <t>Represented as showError() action in self-transitions on override substates</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E54" s="6" t="n"/>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D55" s="28" t="inlineStr">
         <is>
-          <t>Represented as H history state within Shopping composite state</t>
+          <t>History state present</t>
         </is>
       </c>
       <c r="E55" s="6" t="n"/>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>Represented as TimeoutWarning state</t>
+          <t>State present</t>
         </is>
       </c>
       <c r="E56" s="6" t="n"/>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="D57" s="28" t="inlineStr">
         <is>
-          <t>Represented as entry / startCountdown(60s) in TimeoutWarning state note</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E57" s="6" t="n"/>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>Represented as countdownReachedZero transition from TimeoutWarning to ReadyForNextItem</t>
+          <t>Transition present</t>
         </is>
       </c>
       <c r="E58" s="6" t="n"/>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="D59" s="28" t="inlineStr">
         <is>
-          <t>Represented as clearEverything() action in the transition</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E59" s="6" t="n"/>
@@ -7817,11 +7817,11 @@
         </is>
       </c>
       <c r="C60" s="24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>Represented as resetForNextCustomer() action in the transition</t>
+          <t>Missing explicit action but implied by transitioning to Shopping</t>
         </is>
       </c>
       <c r="E60" s="6" t="n"/>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="D61" s="28" t="inlineStr">
         <is>
-          <t>Represented as PaymentProcessing state</t>
+          <t>State present</t>
         </is>
       </c>
       <c r="E61" s="6" t="n"/>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>Represented as paymentFail(error) transition from PaymentProcessing to ReadyForNextItem</t>
+          <t>Transition goes to Shopping which enters Ready</t>
         </is>
       </c>
       <c r="E62" s="6" t="n"/>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D63" s="28" t="inlineStr">
         <is>
-          <t>Represented as showError(error) action</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E63" s="6" t="n"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>Represented as paymentCancel transition from PaymentProcessing to ReadyForNextItem</t>
+          <t>Transition goes to Shopping which enters Ready</t>
         </is>
       </c>
       <c r="E64" s="6" t="n"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D65" s="28" t="inlineStr">
         <is>
-          <t>Represented as paymentSuccess(authCode) transition from PaymentProcessing to ReadyForNextItem</t>
+          <t>Handled via intermediate PrintingBill state</t>
         </is>
       </c>
       <c r="E65" s="6" t="n"/>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>Represented as printBill(authCode) action</t>
+          <t>Action present</t>
         </is>
       </c>
       <c r="E66" s="6" t="n"/>
@@ -7971,11 +7971,11 @@
         </is>
       </c>
       <c r="C67" s="29" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D67" s="28" t="inlineStr">
         <is>
-          <t>Represented as resetForNextCustomer() action</t>
+          <t>Missing explicit action but implied by transitioning to Shopping</t>
         </is>
       </c>
       <c r="E67" s="6" t="n"/>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="D68" s="33" t="inlineStr">
         <is>
-          <t>No additional incorrect states present</t>
+          <t>Reasonable modeling choice to separate printing into its own state</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D69" s="28" t="inlineStr">
         <is>
-          <t>No additional incorrect transitions present</t>
+          <t>Reasonable modeling choice</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>No additional incorrect guards present</t>
+          <t>No incorrect additional guards</t>
         </is>
       </c>
     </row>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="D71" s="28" t="inlineStr">
         <is>
-          <t>No additional incorrect actions present</t>
+          <t>No incorrect additional actions</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>No additional incorrect composite states present</t>
+          <t>Reasonable modeling choice</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="D73" s="28" t="inlineStr">
         <is>
-          <t>No additional incorrect regions present</t>
+          <t>No incorrect additional regions</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>No additional incorrect history states present</t>
+          <t>No incorrect additional history states</t>
         </is>
       </c>
     </row>
@@ -13721,7 +13721,7 @@
     <row r="1" ht="15.75" customHeight="1" s="97">
       <c r="A1" s="98" t="inlineStr">
         <is>
-          <t>Generated by GPT-5</t>
+          <t>Generated by Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="J1" s="42" t="inlineStr">
@@ -13786,15 +13786,15 @@
         <v/>
       </c>
       <c r="C3" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$67, $A3, 'GPT-5 Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D3" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$68:$A$74, $A3, 'GPT-5 Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A3, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E3" s="46">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$67, $A3, 'GPT-5 Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F3" s="46">
@@ -13822,15 +13822,15 @@
         <v/>
       </c>
       <c r="C4" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$67, $A4, 'GPT-5 Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D4" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$68:$A$74, $A4, 'GPT-5 Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A4, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E4" s="46">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$67, $A4, 'GPT-5 Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F4" s="46">
@@ -13862,15 +13862,15 @@
         <v/>
       </c>
       <c r="C5" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$67, $A5, 'GPT-5 Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D5" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$68:$A$74, $A5, 'GPT-5 Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A5, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E5" s="46">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$67, $A5, 'GPT-5 Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F5" s="46">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="J5" s="25" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -13902,15 +13902,15 @@
         <v/>
       </c>
       <c r="C6" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$67, $A6, 'GPT-5 Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D6" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$68:$A$74, $A6, 'GPT-5 Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A6, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E6" s="46">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$67, $A6, 'GPT-5 Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F6" s="46">
@@ -13937,11 +13937,11 @@
         <v/>
       </c>
       <c r="C7" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$67, $A7, 'GPT-5 Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D7" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$68:$A$74, $A7, 'GPT-5 Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A7, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="F7" s="46">
@@ -13973,15 +13973,15 @@
         <v/>
       </c>
       <c r="C8" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$67, $A8, 'GPT-5 Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D8" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$68:$A$74, $A8, 'GPT-5 Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A8, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E8" s="46">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$67, $A7, 'GPT-5 Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F8" s="46">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="J8" s="95" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -14013,15 +14013,15 @@
         <v/>
       </c>
       <c r="C9" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$67, $A9, 'GPT-5 Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D9" s="46">
-        <f>SUMIF('GPT-5 Generation'!$A$68:$A$74, $A9, 'GPT-5 Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A9, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E9" s="46">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$67, $A9, 'GPT-5 Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F9" s="46">

--- a/SSC7/Grading/2 stage/6-examples/SSC7_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/SSC7/Grading/2 stage/6-examples/SSC7_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="SSC7" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gemini 3.1 Pro Grading" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -13786,15 +13786,15 @@
         <v/>
       </c>
       <c r="C3" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D3" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A3, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$68:$A$74, $A3, 'Gemini 3.1 Pro Grading'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E3" s="46">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F3" s="46">
@@ -13822,15 +13822,15 @@
         <v/>
       </c>
       <c r="C4" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D4" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A4, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$68:$A$74, $A4, 'Gemini 3.1 Pro Grading'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E4" s="46">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F4" s="46">
@@ -13862,15 +13862,15 @@
         <v/>
       </c>
       <c r="C5" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D5" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A5, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$68:$A$74, $A5, 'Gemini 3.1 Pro Grading'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E5" s="46">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F5" s="46">
@@ -13902,15 +13902,15 @@
         <v/>
       </c>
       <c r="C6" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D6" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A6, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$68:$A$74, $A6, 'Gemini 3.1 Pro Grading'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E6" s="46">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F6" s="46">
@@ -13937,11 +13937,11 @@
         <v/>
       </c>
       <c r="C7" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D7" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A7, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$68:$A$74, $A7, 'Gemini 3.1 Pro Grading'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="F7" s="46">
@@ -13973,15 +13973,15 @@
         <v/>
       </c>
       <c r="C8" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D8" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A8, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$68:$A$74, $A8, 'Gemini 3.1 Pro Grading'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E8" s="46">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F8" s="46">
@@ -14013,15 +14013,15 @@
         <v/>
       </c>
       <c r="C9" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$67)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$67)</f>
         <v/>
       </c>
       <c r="D9" s="46">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$68:$A$74, $A9, 'Gemini 3.1 Pro Generation'!$C$68:$C$74)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$68:$A$74, $A9, 'Gemini 3.1 Pro Grading'!$C$68:$C$74)</f>
         <v/>
       </c>
       <c r="E9" s="46">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$67, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$67,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$67, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$67,0)</f>
         <v/>
       </c>
       <c r="F9" s="46">
